--- a/brt_config_files/current_config/data/scenario3/scenario3_fqi_results.xlsx
+++ b/brt_config_files/current_config/data/scenario3/scenario3_fqi_results.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25 14:53:28</t>
+          <t>2026-07-29 00:28:58</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>139.6</v>
+        <v>147.62</v>
       </c>
     </row>
     <row r="4">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8376</v>
+        <v>8857</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>22.23</v>
+        <v>19.86</v>
       </c>
     </row>
     <row r="9">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>30.35</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="10">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>10.06</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="11">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12">
@@ -719,22 +719,22 @@
         <v>1</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>24.31</v>
+        <v>23.88</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0.5062</v>
+        <v>0.5216</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.5356</v>
+        <v>6.9188</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -763,22 +763,22 @@
         <v>361</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>24.75</v>
+        <v>23.89</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0.4901</v>
+        <v>0.5301</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.1462</v>
+        <v>5.9933</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
         <v>721</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>35.38</v>
+        <v>35.376</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>24.18</v>
+        <v>24.54</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0.5024</v>
+        <v>0.4773</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.4794</v>
+        <v>7.2015</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -851,22 +851,22 @@
         <v>1081</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>35.372</v>
+        <v>35.374</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.6</v>
+        <v>24.02</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>0.4819</v>
+        <v>0.5097</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>8.5433</v>
+        <v>6.278</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -895,22 +895,22 @@
         <v>1441</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>35.372</v>
+        <v>35.376</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>24.11</v>
+        <v>23.53</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0.4822</v>
+        <v>0.5122</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.3566</v>
+        <v>3.7411</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -939,22 +939,22 @@
         <v>1801</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>35.372</v>
+        <v>35.374</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>25.34</v>
+        <v>22.8</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0.4401</v>
+        <v>0.5849</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>6.1797</v>
+        <v>6.3132</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -983,22 +983,22 @@
         <v>2161</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>35.372</v>
+        <v>35.38</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>24.91</v>
+        <v>22.91</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0.4732</v>
+        <v>0.5722</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>7.8483</v>
+        <v>6.8129</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -1027,22 +1027,22 @@
         <v>2521</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>35.372</v>
+        <v>35.374</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>25.9</v>
+        <v>23.47</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>0.4226</v>
+        <v>0.5493</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>9.7325</v>
+        <v>5.5323</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -1071,22 +1071,22 @@
         <v>2881</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>35.374</v>
+        <v>35.372</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>25.11</v>
+        <v>23.69</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0.4534</v>
+        <v>0.5374</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>4.491</v>
+        <v>6.0724</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -1115,22 +1115,22 @@
         <v>3241</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>25.04</v>
+        <v>22.87</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>0.4608</v>
+        <v>0.5767</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>6.633</v>
+        <v>7.2743</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1159,22 +1159,22 @@
         <v>27</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>35.376</v>
+        <v>35.372</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>24.34</v>
+        <v>23.7</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.6744</v>
+        <v>0.6939</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.7052</v>
+        <v>7.1331</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1200,25 +1200,25 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>35.376</v>
+        <v>35.372</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>24.76</v>
+        <v>23.76</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.6521</v>
+        <v>0.6913</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8.005100000000001</v>
+        <v>7.6858</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1244,25 +1244,25 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>751</v>
+        <v>769</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>24.29</v>
+        <v>24.62</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0.6696</v>
+        <v>0.6403</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>9.3642</v>
+        <v>8.2836</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1288,25 +1288,25 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>35.372</v>
+        <v>35.384</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>24.67</v>
+        <v>24.26</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>0.6385</v>
+        <v>0.6726</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>6.9459</v>
+        <v>6.5843</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1332,25 +1332,25 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1481</v>
+        <v>1470</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>24.28</v>
+        <v>23.98</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>0.6735</v>
+        <v>0.6853</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7.2</v>
+        <v>10.9875</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1376,25 +1376,25 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>35.374</v>
+        <v>35.384</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>25.19</v>
+        <v>22.84</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0.6218</v>
+        <v>0.7607</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8.2058</v>
+        <v>3.5626</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1420,25 +1420,25 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2187</v>
+        <v>2197</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>24.73</v>
+        <v>23.11</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.64</v>
+        <v>0.7372</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9.001099999999999</v>
+        <v>6.2473</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1467,22 +1467,22 @@
         <v>2547</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>35.376</v>
+        <v>35.384</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>25.61</v>
+        <v>23.38</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.7184</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>3.7171</v>
+        <v>6.2472</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2911</v>
+        <v>2927</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>35.38</v>
+        <v>35.372</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>25.19</v>
+        <v>23.63</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0.5773</v>
+        <v>0.6933</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>5.2272</v>
+        <v>5.515</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1552,25 +1552,25 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3267</v>
+        <v>3273</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>35.372</v>
+        <v>35.384</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>25.14</v>
+        <v>23.08</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.6273</v>
+        <v>0.7432</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9.7417</v>
+        <v>6.5525</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1596,25 +1596,25 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>35.384</v>
+        <v>35.38</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>24.41</v>
+        <v>23.99</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0.6734</v>
+        <v>0.6926</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9.7883</v>
+        <v>5.582</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1640,25 +1640,25 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>35.384</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>24.36</v>
+        <v>23.7</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0.6582</v>
+        <v>0.6979</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.9043</v>
+        <v>6.196</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1684,25 +1684,25 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>781</v>
+        <v>810</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>24.19</v>
+        <v>24.55</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>12</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0.6793</v>
+        <v>0.6401</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4.8613</v>
+        <v>6.4387</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1728,25 +1728,25 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>24.71</v>
+        <v>24.27</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>0.6385</v>
+        <v>0.6702</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>6.5856</v>
+        <v>8.8386</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1772,25 +1772,25 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1511</v>
+        <v>1500</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>35.376</v>
+        <v>35.372</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>24.06</v>
+        <v>23.74</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0.6943</v>
+        <v>0.6921</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>6.9459</v>
+        <v>6.0416</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1816,25 +1816,25 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1866</v>
+        <v>1872</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>24.99</v>
+        <v>22.79</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>0.6217</v>
+        <v>0.7568</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>4.1147</v>
+        <v>6.3968</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1860,25 +1860,25 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>2216</v>
+        <v>2230</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>35.372</v>
+        <v>35.374</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>24.51</v>
+        <v>23.06</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>0.65</v>
+        <v>0.7423</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7.6911</v>
+        <v>6.7812</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1904,25 +1904,25 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2576</v>
+        <v>2584</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>35.384</v>
+        <v>35.372</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>26.12</v>
+        <v>23.45</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>0.5907</v>
+        <v>0.7189</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.9134</v>
+        <v>4.8521</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -1948,25 +1948,25 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2941</v>
+        <v>2969</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>25.34</v>
+        <v>23.69</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0.6302</v>
+        <v>0.7074</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>7.3474</v>
+        <v>8.3774</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -1992,25 +1992,25 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>3296</v>
+        <v>3307</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>35.372</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>24.8</v>
+        <v>22.69</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>0.6152</v>
+        <v>0.7376</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7.3217</v>
+        <v>7.0323</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2070,14 +2070,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>11738852154</t>
+          <t>3430028803</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.43</v>
+        <v>6.57</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.23</v>
+        <v>23.6</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>530</v>
@@ -2091,17 +2091,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12909444330</t>
+          <t>299632113</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8.51</v>
+        <v>4.75</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>648</v>
+        <v>518</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2512738712</t>
+          <t>2639664135</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5.77</v>
+        <v>4.86</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -2133,17 +2133,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>299632113</t>
+          <t>12121829931</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4.4</v>
+        <v>0.01</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>519</v>
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>3.66</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2639664135</t>
+          <t>3478026415</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>3.31</v>
+        <v>2.46</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>507</v>
+        <v>533</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -2217,17 +2217,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>3478020599</t>
+          <t>2512738712</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.17</v>
+        <v>2.33</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>48</v>
+        <v>529</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -2238,17 +2238,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>3478026415</t>
+          <t>12909444330</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.5</v>
+        <v>0.64</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1.87</v>
+        <v>2.87</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>517</v>
+        <v>658</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
@@ -2259,17 +2259,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>13134580218</t>
+          <t>12238461185</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1.17</v>
+        <v>0.14</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>349</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -2280,17 +2280,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2512738716</t>
+          <t>2271259942</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1.26</v>
+        <v>0.09</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>398</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -2301,17 +2301,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>12121829931</t>
+          <t>282071079</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.01</v>
+        <v>1.07</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2</v>
+        <v>383</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -2322,17 +2322,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>1785959222</t>
+          <t>6063227845</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -2343,17 +2343,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>2512738758</t>
+          <t>1785959222</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1.02</v>
+        <v>0.03</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>357</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
@@ -2364,17 +2364,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2271259942</t>
+          <t>2271259943</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -2385,17 +2385,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>11738852149</t>
+          <t>6055482982</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.89</v>
+        <v>0.05</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>338</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -2406,17 +2406,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>6055244898</t>
+          <t>3478050366</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
         <v>0.35</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>0.1</v>
+        <v>0.95</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>39</v>
+        <v>402</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
@@ -2431,13 +2431,13 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="C19" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
@@ -2448,17 +2448,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>1785959154</t>
+          <t>11738852154</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>0.05</v>
+        <v>1.14</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>23</v>
+        <v>530</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -2469,17 +2469,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>1833486490</t>
+          <t>4289542433</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.05</v>
+        <v>0.44</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>21</v>
+        <v>203</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -2490,17 +2490,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13134003456</t>
+          <t>1247665033</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
         <v>0.31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1.03</v>
+        <v>0.39</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>464</v>
+        <v>185</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
@@ -2515,13 +2515,13 @@
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -2532,17 +2532,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>12238461185</t>
+          <t>13134003455</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -2553,17 +2553,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>1246355167</t>
+          <t>3478020599</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.79</v>
+        <v>0.12</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>375</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
@@ -2574,17 +2574,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>1247665033</t>
+          <t>11738852149</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>169</v>
+        <v>380</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
@@ -2595,17 +2595,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>11516609609</t>
+          <t>1833486490</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -2616,17 +2616,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>4696818422</t>
+          <t>1670386822</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -2637,17 +2637,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>6055482982</t>
+          <t>2512738758</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>0.05</v>
+        <v>0.59</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>26</v>
+        <v>353</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2658,17 +2658,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>13134003455</t>
+          <t>11919898578</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="C30" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
@@ -2679,17 +2679,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>9884618525</t>
+          <t>1246355167</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>655</v>
+        <v>363</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2700,17 +2700,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>4289542433</t>
+          <t>1247665627</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>0.32</v>
+        <v>0.04</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>179</v>
+        <v>27</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -2721,17 +2721,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>1247665627</t>
+          <t>5935647076</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>0.04</v>
+        <v>0.82</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>24</v>
+        <v>515</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2742,17 +2742,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>2271259943</t>
+          <t>669224144</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2763,17 +2763,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>1246355189</t>
+          <t>9884618525</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>0.03</v>
+        <v>1.01</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>20</v>
+        <v>655</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2784,17 +2784,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>1670386822</t>
+          <t>4696818422</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>0.22</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -2805,17 +2805,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>339225135</t>
+          <t>1246355189</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>0.86</v>
+        <v>0.03</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>550</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
@@ -2826,17 +2826,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>7556478690</t>
+          <t>1247664991</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>224</v>
+        <v>130</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -2847,17 +2847,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>1169044590</t>
+          <t>1247665037</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>0.39</v>
+        <v>0.03</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -2868,17 +2868,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>1247664987</t>
+          <t>11516632609</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>0.64</v>
+        <v>0.02</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>422</v>
+        <v>16</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -2889,17 +2889,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>1247664991</t>
+          <t>299639758</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -2910,17 +2910,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>282071079</t>
+          <t>3430028812</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>0.45</v>
+        <v>0.01</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>304</v>
+        <v>5</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -2931,17 +2931,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>299627271</t>
+          <t>4697885965</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C43" s="2" t="n">
         <v>0.21</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>0.05</v>
-      </c>
       <c r="D43" s="2" t="n">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -2952,11 +2952,11 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>6063227845</t>
+          <t>1247664812</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="C44" s="2" t="n">
         <v>0.02</v>
@@ -2973,17 +2973,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>669224144</t>
+          <t>1247664987</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>0.06</v>
+        <v>0.55</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>42</v>
+        <v>436</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -2994,17 +2994,17 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11919898578</t>
+          <t>1247665192</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3015,17 +3015,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>1247665360</t>
+          <t>13131375762</t>
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -3036,17 +3036,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>13134003461</t>
+          <t>13134580209</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -3057,17 +3057,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>4697885965</t>
+          <t>13134580218</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>1247664812</t>
+          <t>1785959154</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
@@ -3088,7 +3088,7 @@
         <v>0.03</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3099,17 +3099,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>1247664943</t>
+          <t>299627271</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
         <v>0.19</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>1247665021</t>
+          <t>6055244898</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
@@ -3130,7 +3130,7 @@
         <v>0.06</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3141,17 +3141,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13131397858</t>
+          <t>7556478690</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
         <v>0.19</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>24</v>
+        <v>246</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -3162,17 +3162,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>13134580209</t>
+          <t>10915994985</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>0.19</v>
+        <v>0.02</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>139</v>
+        <v>19</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -3183,17 +3183,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>1654424480</t>
+          <t>1247664943</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="C55" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -3204,17 +3204,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>2607936408</t>
+          <t>1247665021</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3225,17 +3225,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11516632609</t>
+          <t>1247665301</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -3246,17 +3246,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>12909444338</t>
+          <t>2607936408</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>121</v>
+        <v>36</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>299639758</t>
+          <t>4697920648</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
@@ -3288,17 +3288,17 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>3663535282</t>
+          <t>6047005881</t>
         </is>
       </c>
       <c r="B60" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>70649445</t>
+          <t>11738664186</t>
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>0.05</v>
+        <v>0.63</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>38</v>
+        <v>536</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>1246355176</t>
+          <t>1247665486</t>
         </is>
       </c>
       <c r="B62" s="2" t="n">
@@ -3340,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
@@ -3351,17 +3351,17 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>13131375765</t>
+          <t>13134003461</t>
         </is>
       </c>
       <c r="B63" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -3393,17 +3393,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>3430028799</t>
+          <t>5526343912</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>0.01</v>
+        <v>0.53</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>9</v>
+        <v>461</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>3430028803</t>
+          <t>2512738716</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>0.64</v>
+        <v>0.24</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>530</v>
+        <v>229</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
@@ -3435,17 +3435,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>11516632601</t>
+          <t>3663535282</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
@@ -3456,17 +3456,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>2587043102</t>
+          <t>70649445</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>0.49</v>
+        <v>0.03</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>416</v>
+        <v>30</v>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
@@ -3477,17 +3477,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>4697920632</t>
+          <t>1169044590</t>
         </is>
       </c>
       <c r="B69" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>465</v>
+        <v>238</v>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
@@ -3498,17 +3498,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>4697920648</t>
+          <t>12280837962</t>
         </is>
       </c>
       <c r="B70" s="2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
@@ -3519,17 +3519,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>5935647076</t>
+          <t>11516609609</t>
         </is>
       </c>
       <c r="B71" s="2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>0.57</v>
+        <v>0.05</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>489</v>
+        <v>55</v>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
@@ -3540,17 +3540,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>6047005881</t>
+          <t>1247665101</t>
         </is>
       </c>
       <c r="B72" s="2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -3561,17 +3561,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>70650627</t>
+          <t>13131375765</t>
         </is>
       </c>
       <c r="B73" s="2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
@@ -3582,17 +3582,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>10915994985</t>
+          <t>3478020616</t>
         </is>
       </c>
       <c r="B74" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
@@ -3603,17 +3603,17 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>11738664186</t>
+          <t>12280837959</t>
         </is>
       </c>
       <c r="B75" s="2" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>0.54</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>504</v>
+        <v>76</v>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
@@ -3624,17 +3624,17 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>5526343912</t>
+          <t>13134580212</t>
         </is>
       </c>
       <c r="B76" s="2" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>451</v>
+        <v>35</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
@@ -3645,17 +3645,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>10915994990</t>
+          <t>1654424042</t>
         </is>
       </c>
       <c r="B77" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>302</v>
+        <v>50</v>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
@@ -3666,17 +3666,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>1247665301</t>
+          <t>2142757871</t>
         </is>
       </c>
       <c r="B78" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -3687,17 +3687,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13134003460</t>
+          <t>339225135</t>
         </is>
       </c>
       <c r="B79" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>457</v>
+        <v>554</v>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>564627859</t>
+          <t>4995658238</t>
         </is>
       </c>
       <c r="B80" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
@@ -3729,17 +3729,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>13131375762</t>
+          <t>10915994990</t>
         </is>
       </c>
       <c r="B81" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>29</v>
+        <v>298</v>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
@@ -3750,17 +3750,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>3478020616</t>
+          <t>11516632600</t>
         </is>
       </c>
       <c r="B82" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
@@ -3771,17 +3771,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>3478050376</t>
+          <t>12909444338</t>
         </is>
       </c>
       <c r="B83" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
@@ -3792,17 +3792,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>4995658238</t>
+          <t>13134003457</t>
         </is>
       </c>
       <c r="B84" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
@@ -3813,17 +3813,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>1247665037</t>
+          <t>2587043102</t>
         </is>
       </c>
       <c r="B85" s="2" t="n">
         <v>0.12</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>16</v>
+        <v>440</v>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
@@ -3834,17 +3834,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>1247665192</t>
+          <t>3478050376</t>
         </is>
       </c>
       <c r="B86" s="2" t="n">
         <v>0.12</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
@@ -3855,17 +3855,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>9817149191</t>
+          <t>4995658236</t>
         </is>
       </c>
       <c r="B87" s="2" t="n">
         <v>0.12</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>0.46</v>
+        <v>0.03</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>530</v>
+        <v>39</v>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
@@ -3876,17 +3876,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>1247665101</t>
+          <t>564627859</t>
         </is>
       </c>
       <c r="B88" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>13134580212</t>
+          <t>1661742603</t>
         </is>
       </c>
       <c r="B89" s="2" t="n">
@@ -3907,7 +3907,7 @@
         <v>0.03</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
@@ -3918,17 +3918,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>2142757871</t>
+          <t>3478053500</t>
         </is>
       </c>
       <c r="B90" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
@@ -3939,17 +3939,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>3441398845</t>
+          <t>4697920632</t>
         </is>
       </c>
       <c r="B91" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>0.01</v>
+        <v>0.34</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>16</v>
+        <v>477</v>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
@@ -3960,17 +3960,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>4696835286</t>
+          <t>9817149191</t>
         </is>
       </c>
       <c r="B92" s="2" t="n">
         <v>0.11</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>299</v>
+        <v>530</v>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
@@ -3981,17 +3981,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>4696836111</t>
+          <t>1247665360</t>
         </is>
       </c>
       <c r="B93" s="2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="C93" s="2" t="n">
         <v>0.02</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
@@ -4002,17 +4002,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>6060574286</t>
+          <t>13131397858</t>
         </is>
       </c>
       <c r="B94" s="2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>0.31</v>
+        <v>0.02</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>406</v>
+        <v>31</v>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11738664240</t>
+          <t>1654424480</t>
         </is>
       </c>
       <c r="B95" s="2" t="n">
@@ -4033,7 +4033,7 @@
         <v>0.01</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
@@ -4044,17 +4044,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>1247665364</t>
+          <t>3441398845</t>
         </is>
       </c>
       <c r="B96" s="2" t="n">
         <v>0.1</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>0.22</v>
+        <v>0.01</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>307</v>
+        <v>10</v>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>1654424042</t>
+          <t>70650627</t>
         </is>
       </c>
       <c r="B97" s="2" t="n">
@@ -4075,7 +4075,7 @@
         <v>0.03</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
@@ -4086,17 +4086,17 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>3430028802</t>
+          <t>11516632601</t>
         </is>
       </c>
       <c r="B98" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>3430028812</t>
+          <t>13134003456</t>
         </is>
       </c>
       <c r="B99" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>5</v>
+        <v>453</v>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
@@ -4128,17 +4128,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>3663502693</t>
+          <t>13134003460</t>
         </is>
       </c>
       <c r="B100" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>159</v>
+        <v>423</v>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
@@ -4149,17 +4149,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>3663502700</t>
+          <t>3441398795</t>
         </is>
       </c>
       <c r="B101" s="2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>0.47</v>
+        <v>0.03</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>640</v>
+        <v>48</v>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
@@ -4170,17 +4170,17 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>11516632600</t>
+          <t>3663502693</t>
         </is>
       </c>
       <c r="B102" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>0.02</v>
+        <v>0.1</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>29</v>
+        <v>163</v>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
@@ -4191,17 +4191,17 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>12280837959</t>
+          <t>11516632573</t>
         </is>
       </c>
       <c r="B103" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>0.02</v>
+        <v>0.12</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>37</v>
+        <v>206</v>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
@@ -4212,17 +4212,17 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>13131397862</t>
+          <t>1247665364</t>
         </is>
       </c>
       <c r="B104" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>367</v>
+        <v>314</v>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
@@ -4233,17 +4233,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>1661742603</t>
+          <t>12909444328</t>
         </is>
       </c>
       <c r="B105" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
@@ -4254,17 +4254,17 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>4198760294</t>
+          <t>1664599992</t>
         </is>
       </c>
       <c r="B106" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>28</v>
+        <v>514</v>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
@@ -4275,17 +4275,17 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>4696818416</t>
+          <t>3663502700</t>
         </is>
       </c>
       <c r="B107" s="2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>439</v>
+        <v>631</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -4296,17 +4296,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>1247665486</t>
+          <t>4198760294</t>
         </is>
       </c>
       <c r="B108" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
@@ -4317,17 +4317,17 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>12909444328</t>
+          <t>11516632582</t>
         </is>
       </c>
       <c r="B109" s="2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>18</v>
+        <v>208</v>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
@@ -4338,17 +4338,17 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>1438438595</t>
+          <t>3430028802</t>
         </is>
       </c>
       <c r="B110" s="2" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>0.09</v>
+        <v>0.05</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>150</v>
+        <v>97</v>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
@@ -4359,17 +4359,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>11516632573</t>
+          <t>3478050372</t>
         </is>
       </c>
       <c r="B111" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>200</v>
+        <v>33</v>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
@@ -4380,17 +4380,17 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>11516632582</t>
+          <t>4696836111</t>
         </is>
       </c>
       <c r="B112" s="2" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>282</v>
+        <v>25</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -4401,17 +4401,17 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>1664599992</t>
+          <t>13131375767</t>
         </is>
       </c>
       <c r="B113" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>0.24</v>
+        <v>0.05</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>507</v>
+        <v>133</v>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
@@ -4422,17 +4422,17 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>2591388559</t>
+          <t>1761421863</t>
         </is>
       </c>
       <c r="B114" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>0.03</v>
+        <v>0.26</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>53</v>
+        <v>619</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -4443,17 +4443,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>3478050366</t>
+          <t>3430028799</t>
         </is>
       </c>
       <c r="B115" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>406</v>
+        <v>6</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -4464,17 +4464,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>4995658232</t>
+          <t>4696835286</t>
         </is>
       </c>
       <c r="B116" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>9</v>
+        <v>349</v>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
@@ -4485,17 +4485,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>13131375764</t>
+          <t>6057358075</t>
         </is>
       </c>
       <c r="B117" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>422</v>
+        <v>561</v>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>4995658236</t>
+          <t>6060574286</t>
         </is>
       </c>
       <c r="B118" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>30</v>
+        <v>427</v>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
@@ -4527,17 +4527,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>6057358075</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="B119" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>558</v>
+        <v>42</v>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
@@ -4548,17 +4548,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>13134003457</t>
+          <t>11738664161</t>
         </is>
       </c>
       <c r="B120" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>35</v>
+        <v>545</v>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
@@ -4569,17 +4569,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>1761421863</t>
+          <t>11738664240</t>
         </is>
       </c>
       <c r="B121" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>572</v>
+        <v>14</v>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
@@ -4590,17 +4590,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>6027310523</t>
+          <t>13131375764</t>
         </is>
       </c>
       <c r="B122" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>0.1</v>
+        <v>0.16</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>286</v>
+        <v>466</v>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
@@ -4611,17 +4611,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>11516632572</t>
+          <t>13131397862</t>
         </is>
       </c>
       <c r="B123" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C123" s="2" t="n">
         <v>0.08</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
@@ -4632,17 +4632,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>11738664161</t>
+          <t>13134580214</t>
         </is>
       </c>
       <c r="B124" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>539</v>
+        <v>16</v>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
@@ -4653,17 +4653,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>11738664244</t>
+          <t>1438438595</t>
         </is>
       </c>
       <c r="B125" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
@@ -4674,17 +4674,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>13134003463</t>
+          <t>6058348491</t>
         </is>
       </c>
       <c r="B126" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>583</v>
+        <v>208</v>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
@@ -4695,17 +4695,17 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>3441398795</t>
+          <t>11738664244</t>
         </is>
       </c>
       <c r="B127" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
@@ -4716,7 +4716,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>3478050372</t>
+          <t>12909444326</t>
         </is>
       </c>
       <c r="B128" s="2" t="n">
@@ -4726,7 +4726,7 @@
         <v>0</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
@@ -4737,17 +4737,17 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>6058348491</t>
+          <t>2591388559</t>
         </is>
       </c>
       <c r="B129" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="D129" s="2" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
@@ -4758,17 +4758,17 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>60881778</t>
+          <t>6027310523</t>
         </is>
       </c>
       <c r="B130" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="D130" s="2" t="n">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
@@ -4779,17 +4779,17 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>13131375767</t>
+          <t>13134003463</t>
         </is>
       </c>
       <c r="B131" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="D131" s="2" t="n">
-        <v>129</v>
+        <v>592</v>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
@@ -4821,17 +4821,17 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>3478053500</t>
+          <t>4696818416</t>
         </is>
       </c>
       <c r="B133" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D133" s="2" t="n">
-        <v>19</v>
+        <v>355</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -4842,17 +4842,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>12280837956</t>
+          <t>60881778</t>
         </is>
       </c>
       <c r="B134" s="2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C134" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="D134" s="2" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
@@ -4863,17 +4863,17 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>11516632572</t>
         </is>
       </c>
       <c r="B135" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D135" s="2" t="n">
-        <v>39</v>
+        <v>242</v>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
@@ -4884,17 +4884,17 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>12280837962</t>
+          <t>4995658232</t>
         </is>
       </c>
       <c r="B136" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C136" s="2" t="n">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>1247665043</t>
+          <t>12280837956</t>
         </is>
       </c>
       <c r="B137" s="2" t="n">
@@ -4915,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>1247665180</t>
+          <t>1246355176</t>
         </is>
       </c>
       <c r="B138" s="2" t="n">
@@ -4936,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>1247665955</t>
+          <t>1247665043</t>
         </is>
       </c>
       <c r="B139" s="2" t="n">
@@ -4968,7 +4968,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>12909444326</t>
+          <t>1247665180</t>
         </is>
       </c>
       <c r="B140" s="2" t="n">
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>12909444335</t>
+          <t>1247665955</t>
         </is>
       </c>
       <c r="B141" s="2" t="n">
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>13134580214</t>
+          <t>12909444335</t>
         </is>
       </c>
       <c r="B142" s="2" t="n">
@@ -5020,7 +5020,7 @@
         <v>0</v>
       </c>
       <c r="D142" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>0</v>
       </c>
       <c r="D144" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="D145" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
@@ -5209,7 +5209,7 @@
         <v>0</v>
       </c>
       <c r="D151" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
